--- a/output/pdf_financials_xlsx/TDG.xlsx
+++ b/output/pdf_financials_xlsx/TDG.xlsx
@@ -3375,28 +3375,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0424</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0424</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.823534</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.352328</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.677186</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.180901</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.195516</v>
       </c>
     </row>
     <row r="93">
@@ -5516,7 +5516,11 @@
           <t>Reserve 14</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6324,7 +6328,11 @@
           <t>Reserve 13</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -7264,7 +7272,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -7880,7 +7892,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.0424</v>
       </c>
@@ -17168,7 +17184,7 @@
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.108406</v>
+        <v>-0.108406</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TDG.xlsx
+++ b/output/pdf_financials_xlsx/TDG.xlsx
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008234999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002973</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.228342</v>
       </c>
     </row>
     <row r="13">
@@ -1265,10 +1265,10 @@
         <v>-0.342949</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.831816</v>
+        <v>-4.840051</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-11.545303</v>
+        <v>-11.548276</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-6.716358</v>
@@ -1277,7 +1277,7 @@
         <v>-4.595543</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.965873</v>
+        <v>-7.194215</v>
       </c>
     </row>
     <row r="28">
@@ -1327,10 +1327,10 @@
         <v>-0.342949</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.819262</v>
+        <v>-4.827497</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-11.492471</v>
+        <v>-11.495444</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-6.618158</v>
@@ -1339,7 +1339,7 @@
         <v>-4.492577</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.858237</v>
+        <v>-7.086579</v>
       </c>
     </row>
     <row r="30">
@@ -1481,28 +1481,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.193809</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.145669</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.822505</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.810269</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.961007</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.588712</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.714714</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>40.679303</v>
       </c>
     </row>
     <row r="35">
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.193809</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.145669</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.822505</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.810269</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.961007</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.588712</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.714714</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>40.679303</v>
       </c>
     </row>
     <row r="37">
@@ -1921,22 +1921,22 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.886288</v>
+        <v>0.06378300000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.083368</v>
+        <v>0.273099</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.20524</v>
+        <v>0.244233</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.656398</v>
+        <v>0.067686</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.961135</v>
+        <v>0.246421</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.79956</v>
+        <v>1.120257</v>
       </c>
     </row>
     <row r="49">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5166,7 +5166,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -5952,7 +5956,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -6440,7 +6448,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6552,7 +6560,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6832,7 +6840,11 @@
           <t>Reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7542,7 +7554,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -10718,7 +10730,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -14124,7 +14140,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15154,7 +15170,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -15700,7 +15716,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">

--- a/output/pdf_financials_xlsx/TDG.xlsx
+++ b/output/pdf_financials_xlsx/TDG.xlsx
@@ -610,22 +610,22 @@
         <v>0.024505</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.074</v>
+        <v>0.084511</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.485203</v>
+        <v>0.53601</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.896461</v>
+        <v>1.064276</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.937132</v>
+        <v>1.257964</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.877969</v>
+        <v>1.172482</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.045472</v>
+        <v>1.309015</v>
       </c>
     </row>
     <row r="8">
@@ -3930,19 +3930,19 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.002146</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.003707</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.005379</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.02675</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.009561</v>
       </c>
     </row>
     <row r="111">
@@ -3961,19 +3961,19 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.251075</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039232</v>
       </c>
     </row>
     <row r="112">
@@ -4696,19 +4696,19 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.251075</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039232</v>
       </c>
     </row>
     <row r="135">
@@ -4731,19 +4731,19 @@
         <v>-0.351501</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-3.093112</v>
+        <v>-3.344187</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-13.066905</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-8.589836</v>
+        <v>-8.689336000000001</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-5.506889</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-5.747677</v>
+        <v>-5.786909</v>
       </c>
     </row>
   </sheetData>
@@ -8366,7 +8366,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -8984,7 +8988,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -10230,7 +10238,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10904,7 +10916,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -11630,7 +11646,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -12656,7 +12676,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>0.258579</v>
       </c>
@@ -13244,7 +13268,11 @@
           <t>Proceeds from share issuance (Note 5)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.258579</v>
       </c>
@@ -13512,7 +13540,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -13620,7 +13652,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -14506,7 +14542,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14836,7 +14876,11 @@
           <t>Director fees 16</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -15446,7 +15490,11 @@
           <t>Director fees 17</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
